--- a/unified_metrics_svm.xlsx
+++ b/unified_metrics_svm.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u0186653/Desktop/research/dingen/deepnir/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9C1FB9-092C-C64E-882B-9C3E6CF3CC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-20" yWindow="660" windowWidth="17280" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -79,12 +85,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,15 +127,34 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -167,7 +192,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -201,6 +226,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -235,9 +261,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,20 +437,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -446,7 +473,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -460,16 +487,16 @@
         <v>0.6386478555636449</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0908236476865921</v>
+        <v>9.0823647686592096E-2</v>
       </c>
       <c r="F2" s="2">
-        <v>4.125938728656514</v>
+        <v>4.1259387286565143</v>
       </c>
       <c r="G2" s="2">
-        <v>0.0137334156354908</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>1.3733415635490799E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -480,19 +507,19 @@
         <v>18</v>
       </c>
       <c r="D3" s="1">
-        <v>0.1841155852047316</v>
+        <v>0.18411558520473159</v>
       </c>
       <c r="E3" s="2">
-        <v>0.1239329168529018</v>
+        <v>0.12393291685290179</v>
       </c>
       <c r="F3" s="2">
-        <v>0.32124912408735</v>
+        <v>0.32124912408735001</v>
       </c>
       <c r="G3" s="2">
-        <v>-0.0668530306947084</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>-6.6853030694708396E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -503,19 +530,19 @@
         <v>18</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.0342389563807947</v>
+        <v>-3.4238956380794702E-2</v>
       </c>
       <c r="E4" s="2">
         <v>0.2041076577763262</v>
       </c>
       <c r="F4" s="2">
-        <v>0.1871991074889778</v>
+        <v>0.18719910748897781</v>
       </c>
       <c r="G4" s="2">
-        <v>-0.0252564329659356</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>-2.5256432965935601E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -526,19 +553,19 @@
         <v>19</v>
       </c>
       <c r="D5" s="1">
-        <v>0.5786983316156765</v>
+        <v>0.57869833161567652</v>
       </c>
       <c r="E5" s="2">
         <v>0.1058915932512218</v>
       </c>
       <c r="F5" s="2">
-        <v>3.604090846085757</v>
+        <v>3.6040908460857568</v>
       </c>
       <c r="G5" s="2">
-        <v>0.0344712501413288</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>3.4471250141328798E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -549,19 +576,19 @@
         <v>19</v>
       </c>
       <c r="D6" s="1">
-        <v>-0.126484875424325</v>
+        <v>-0.12648487542432499</v>
       </c>
       <c r="E6" s="2">
-        <v>0.1711131550871046</v>
+        <v>0.17111315508710459</v>
       </c>
       <c r="F6" s="2">
-        <v>0.0106851873454719</v>
+        <v>1.06851873454719E-2</v>
       </c>
       <c r="G6" s="2">
         <v>-0.1180665688362208</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -572,19 +599,19 @@
         <v>19</v>
       </c>
       <c r="D7" s="1">
-        <v>0.1490949811873996</v>
+        <v>0.14909498118739961</v>
       </c>
       <c r="E7" s="2">
-        <v>0.1679265988855433</v>
+        <v>0.16792659888554329</v>
       </c>
       <c r="F7" s="2">
         <v>1.114820625390549</v>
       </c>
       <c r="G7" s="2">
-        <v>-0.0648852691096778</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>-6.4885269109677804E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -595,19 +622,19 @@
         <v>18</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.0336620642720821</v>
+        <v>-3.3662064272082098E-2</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0375306344119219</v>
+        <v>3.75306344119219E-2</v>
       </c>
       <c r="F8" s="2">
-        <v>1.156219146643021</v>
+        <v>1.1562191466430209</v>
       </c>
       <c r="G8" s="2">
-        <v>0.0419205173935081</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>4.1920517393508099E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -618,19 +645,19 @@
         <v>18</v>
       </c>
       <c r="D9" s="1">
-        <v>0.6061536917464908</v>
+        <v>0.60615369174649081</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0073489755000056</v>
+        <v>7.3489755000056001E-3</v>
       </c>
       <c r="F9" s="2">
-        <v>10.76606833558044</v>
+        <v>10.766068335580441</v>
       </c>
       <c r="G9" s="2">
-        <v>0.0206405371456457</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>2.0640537145645701E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -641,19 +668,19 @@
         <v>18</v>
       </c>
       <c r="D10" s="1">
-        <v>0.7017399786233512</v>
+        <v>0.70173997862335125</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0197980786661392</v>
+        <v>1.97980786661392E-2</v>
       </c>
       <c r="F10" s="2">
         <v>10.73889073904726</v>
       </c>
       <c r="G10" s="2">
-        <v>0.008582580159146201</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>8.5825801591462008E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -664,19 +691,19 @@
         <v>18</v>
       </c>
       <c r="D11" s="1">
-        <v>0.6916483993746425</v>
+        <v>0.69164839937464251</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0038870684221213</v>
+        <v>3.8870684221213002E-3</v>
       </c>
       <c r="F11" s="2">
         <v>24.05438401370867</v>
       </c>
       <c r="G11" s="2">
-        <v>-0.005963869052925</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>-5.9638690529249996E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -687,19 +714,19 @@
         <v>19</v>
       </c>
       <c r="D12" s="1">
-        <v>0.3565715027742931</v>
+        <v>0.35657150277429311</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0233618708998436</v>
+        <v>2.3361870899843599E-2</v>
       </c>
       <c r="F12" s="2">
-        <v>4.06206639956546</v>
+        <v>4.0620663995654596</v>
       </c>
       <c r="G12" s="2">
-        <v>0.0295794458954955</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>2.95794458954955E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -710,19 +737,19 @@
         <v>19</v>
       </c>
       <c r="D13" s="1">
-        <v>0.2386686983236715</v>
+        <v>0.23866869832367149</v>
       </c>
       <c r="E13" s="2">
-        <v>0.0142060620251019</v>
+        <v>1.42060620251019E-2</v>
       </c>
       <c r="F13" s="2">
-        <v>4.858585648347476</v>
+        <v>4.8585856483474759</v>
       </c>
       <c r="G13" s="2">
-        <v>0.0205075127645465</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>2.0507512764546501E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -733,19 +760,19 @@
         <v>19</v>
       </c>
       <c r="D14" s="1">
-        <v>0.8839995348199047</v>
+        <v>0.88399953481990468</v>
       </c>
       <c r="E14" s="2">
-        <v>0.0076999469266586</v>
+        <v>7.6999469266585997E-3</v>
       </c>
       <c r="F14" s="2">
-        <v>27.89051954661564</v>
+        <v>27.890519546615639</v>
       </c>
       <c r="G14" s="2">
-        <v>0.0200506622430324</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>2.00506622430324E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -756,19 +783,19 @@
         <v>19</v>
       </c>
       <c r="D15" s="1">
-        <v>0.8740329443496473</v>
+        <v>0.87403294434964729</v>
       </c>
       <c r="E15" s="2">
-        <v>0.0015879358604043</v>
+        <v>1.5879358604043001E-3</v>
       </c>
       <c r="F15" s="2">
-        <v>59.76269841713206</v>
+        <v>59.762698417132057</v>
       </c>
       <c r="G15" s="2">
-        <v>0.0031683594496371</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>3.1683594496371001E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -779,19 +806,19 @@
         <v>18</v>
       </c>
       <c r="D16" s="1">
-        <v>0.8717673350705445</v>
+        <v>0.87176733507054449</v>
       </c>
       <c r="E16" s="2">
-        <v>0.1035480158293313</v>
+        <v>0.10354801582933131</v>
       </c>
       <c r="F16" s="2">
-        <v>8.002909455015969</v>
+        <v>8.0029094550159687</v>
       </c>
       <c r="G16" s="2">
-        <v>0.0171238063964222</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>1.7123806396422199E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -802,19 +829,19 @@
         <v>18</v>
       </c>
       <c r="D17" s="1">
-        <v>0.9732015736285972</v>
+        <v>0.97320157362859716</v>
       </c>
       <c r="E17" s="2">
-        <v>0.133743262323482</v>
+        <v>0.13374326232348199</v>
       </c>
       <c r="F17" s="2">
-        <v>16.13999918614464</v>
+        <v>16.139999186144639</v>
       </c>
       <c r="G17" s="2">
-        <v>-0.0501260015372909</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>-5.0126001537290903E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -825,19 +852,19 @@
         <v>18</v>
       </c>
       <c r="D18" s="1">
-        <v>0.8419959366533089</v>
+        <v>0.84199593665330885</v>
       </c>
       <c r="E18" s="2">
-        <v>0.1730185114995046</v>
+        <v>0.17301851149950459</v>
       </c>
       <c r="F18" s="2">
-        <v>4.783794596377254</v>
+        <v>4.7837945963772537</v>
       </c>
       <c r="G18" s="2">
         <v>-0.1044525311867438</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -848,19 +875,19 @@
         <v>18</v>
       </c>
       <c r="D19" s="1">
-        <v>0.9850045250539592</v>
+        <v>0.98500452505395919</v>
       </c>
       <c r="E19" s="2">
         <v>0.1185765314743924</v>
       </c>
       <c r="F19" s="2">
-        <v>23.31494090153264</v>
+        <v>23.314940901532641</v>
       </c>
       <c r="G19" s="2">
         <v>-0.1626205950844696</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -871,19 +898,19 @@
         <v>18</v>
       </c>
       <c r="D20" s="1">
-        <v>0.9036863081602132</v>
+        <v>0.90368630816021323</v>
       </c>
       <c r="E20" s="2">
-        <v>0.2986220110665641</v>
+        <v>0.29862201106656411</v>
       </c>
       <c r="F20" s="2">
-        <v>5.37126612419013</v>
+        <v>5.3712661241901296</v>
       </c>
       <c r="G20" s="2">
-        <v>0.1270872426022575</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>0.12708724260225751</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -894,19 +921,19 @@
         <v>19</v>
       </c>
       <c r="D21" s="1">
-        <v>0.8628993827024511</v>
+        <v>0.86289938270245115</v>
       </c>
       <c r="E21" s="2">
-        <v>0.1107088969721372</v>
+        <v>0.11070889697213721</v>
       </c>
       <c r="F21" s="2">
-        <v>7.328396498237542</v>
+        <v>7.3283964982375416</v>
       </c>
       <c r="G21" s="2">
-        <v>-0.0181415432276517</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>-1.8141543227651699E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -917,19 +944,19 @@
         <v>19</v>
       </c>
       <c r="D22" s="1">
-        <v>0.9668428119178636</v>
+        <v>0.96684281191786359</v>
       </c>
       <c r="E22" s="2">
-        <v>0.1654780188254051</v>
+        <v>0.16547801882540511</v>
       </c>
       <c r="F22" s="2">
-        <v>13.04360345432005</v>
+        <v>13.043603454320049</v>
       </c>
       <c r="G22" s="2">
-        <v>-0.0359847308137381</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>-3.5984730813738097E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -940,19 +967,19 @@
         <v>19</v>
       </c>
       <c r="D23" s="1">
-        <v>0.7676503398824771</v>
+        <v>0.76765033988247711</v>
       </c>
       <c r="E23" s="2">
-        <v>0.2544288513184714</v>
+        <v>0.25442885131847143</v>
       </c>
       <c r="F23" s="2">
-        <v>2.799647059423073</v>
+        <v>2.7996470594230729</v>
       </c>
       <c r="G23" s="2">
-        <v>-0.1378841353751113</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>-0.13788413537511129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -963,19 +990,19 @@
         <v>19</v>
       </c>
       <c r="D24" s="1">
-        <v>0.9846237323940074</v>
+        <v>0.98462373239400736</v>
       </c>
       <c r="E24" s="2">
         <v>0.1215876446929104</v>
       </c>
       <c r="F24" s="2">
-        <v>22.01774872595046</v>
+        <v>22.017748725950462</v>
       </c>
       <c r="G24" s="2">
-        <v>-0.1707637432084221</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>-0.17076374320842211</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -986,19 +1013,19 @@
         <v>19</v>
       </c>
       <c r="D25" s="1">
-        <v>0.9097965098687218</v>
+        <v>0.90979650986872185</v>
       </c>
       <c r="E25" s="2">
-        <v>0.2796772412486606</v>
+        <v>0.27967724124866061</v>
       </c>
       <c r="F25" s="2">
-        <v>5.687965835700248</v>
+        <v>5.6879658357002478</v>
       </c>
       <c r="G25" s="2">
         <v>0.1403934706863782</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -1009,19 +1036,19 @@
         <v>18</v>
       </c>
       <c r="D26" s="1">
-        <v>0.2344039443359152</v>
+        <v>0.23440394433591519</v>
       </c>
       <c r="E26" s="2">
-        <v>0.6041248875603868</v>
+        <v>0.60412488756038685</v>
       </c>
       <c r="F26" s="2">
-        <v>0.8986117663520491</v>
+        <v>0.89861176635204909</v>
       </c>
       <c r="G26" s="2">
         <v>-0.1278601880392406</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -1032,19 +1059,19 @@
         <v>18</v>
       </c>
       <c r="D27" s="1">
-        <v>-0.09464969230054129</v>
+        <v>-9.4649692300541294E-2</v>
       </c>
       <c r="E27" s="2">
-        <v>4.115845852521915</v>
+        <v>4.1158458525219146</v>
       </c>
       <c r="F27" s="2">
-        <v>0.0696601634328793</v>
+        <v>6.9660163432879299E-2</v>
       </c>
       <c r="G27" s="2">
-        <v>-1.007097655991423</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>-1.0070976559914231</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -1055,19 +1082,19 @@
         <v>18</v>
       </c>
       <c r="D28" s="1">
-        <v>-0.5863783681722898</v>
+        <v>-0.58637836817228983</v>
       </c>
       <c r="E28" s="2">
-        <v>2.301253311595057</v>
+        <v>2.3012533115950569</v>
       </c>
       <c r="F28" s="2">
-        <v>0.0386169983725237</v>
+        <v>3.8616998372523699E-2</v>
       </c>
       <c r="G28" s="2">
-        <v>0.6468302953010229</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>0.64683029530102287</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -1078,19 +1105,19 @@
         <v>18</v>
       </c>
       <c r="D29" s="1">
-        <v>0.9189148560061716</v>
+        <v>0.91891485600617162</v>
       </c>
       <c r="E29" s="2">
-        <v>0.0185126062333593</v>
+        <v>1.8512606233359302E-2</v>
       </c>
       <c r="F29" s="2">
-        <v>21.9753464493645</v>
+        <v>21.975346449364501</v>
       </c>
       <c r="G29" s="2">
-        <v>-0.0498543552802366</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>-4.9854355280236601E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1101,19 +1128,19 @@
         <v>19</v>
       </c>
       <c r="D30" s="1">
-        <v>0.0349769312472509</v>
+        <v>3.4976931247250903E-2</v>
       </c>
       <c r="E30" s="2">
-        <v>0.7614909306158055</v>
+        <v>0.76149093061580553</v>
       </c>
       <c r="F30" s="2">
-        <v>0.6814869261415201</v>
+        <v>0.68148692614152007</v>
       </c>
       <c r="G30" s="2">
-        <v>-0.0861898314365528</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>-8.6189831436552802E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -1124,19 +1151,19 @@
         <v>19</v>
       </c>
       <c r="D31" s="1">
-        <v>0.5420208421943076</v>
+        <v>0.54202084219430757</v>
       </c>
       <c r="E31" s="2">
         <v>1.721986157265105</v>
       </c>
       <c r="F31" s="2">
-        <v>0.6012618569960297</v>
+        <v>0.60126185699602974</v>
       </c>
       <c r="G31" s="2">
-        <v>-0.6806005775477424</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>-0.68060057754774239</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -1147,19 +1174,19 @@
         <v>19</v>
       </c>
       <c r="D32" s="1">
-        <v>-0.3537056228263309</v>
+        <v>-0.35370562282633089</v>
       </c>
       <c r="E32" s="2">
         <v>1.96373047562611</v>
       </c>
       <c r="F32" s="2">
-        <v>0.0577187423620417</v>
+        <v>5.7718742362041699E-2</v>
       </c>
       <c r="G32" s="2">
-        <v>0.6396796194671003</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>0.63967961946710028</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -1170,19 +1197,19 @@
         <v>19</v>
       </c>
       <c r="D33" s="1">
-        <v>0.9197620274809551</v>
+        <v>0.91976202748095515</v>
       </c>
       <c r="E33" s="2">
-        <v>0.0183191879183348</v>
+        <v>1.8319187918334801E-2</v>
       </c>
       <c r="F33" s="2">
-        <v>22.50546215150351</v>
+        <v>22.505462151503512</v>
       </c>
       <c r="G33" s="2">
-        <v>-0.040812949069405</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>-4.0812949069404997E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -1193,19 +1220,19 @@
         <v>18</v>
       </c>
       <c r="D34" s="1">
-        <v>0.4737847020968667</v>
+        <v>0.47378470209686668</v>
       </c>
       <c r="E34" s="2">
-        <v>0.704644315144665</v>
+        <v>0.70464431514466497</v>
       </c>
       <c r="F34" s="2">
-        <v>0.892074499943959</v>
+        <v>0.89207449994395904</v>
       </c>
       <c r="G34" s="2">
-        <v>0.1515257083802324</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>0.15152570838023241</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -1216,19 +1243,19 @@
         <v>18</v>
       </c>
       <c r="D35" s="1">
-        <v>0.8514602342423828</v>
+        <v>0.85146023424238282</v>
       </c>
       <c r="E35" s="2">
-        <v>0.0559362699146606</v>
+        <v>5.5936269914660601E-2</v>
       </c>
       <c r="F35" s="2">
-        <v>9.527363677027616</v>
+        <v>9.5273636770276156</v>
       </c>
       <c r="G35" s="2">
-        <v>-0.0075381586049398</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>-7.5381586049398002E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -1239,19 +1266,19 @@
         <v>18</v>
       </c>
       <c r="D36" s="1">
-        <v>0.9061788409628933</v>
+        <v>0.90617884096289325</v>
       </c>
       <c r="E36" s="2">
         <v>0.1939900675241186</v>
       </c>
       <c r="F36" s="2">
-        <v>6.329967654478279</v>
+        <v>6.3299676544782786</v>
       </c>
       <c r="G36" s="2">
-        <v>-0.0298032272240952</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>-2.9803227224095199E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -1262,19 +1289,19 @@
         <v>18</v>
       </c>
       <c r="D37" s="1">
-        <v>0.9614514778038152</v>
+        <v>0.96145147780381524</v>
       </c>
       <c r="E37" s="2">
-        <v>0.3158655124624535</v>
+        <v>0.31586551246245348</v>
       </c>
       <c r="F37" s="2">
         <v>8.452731879775861</v>
       </c>
       <c r="G37" s="2">
-        <v>0.1194710532259455</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>0.11947105322594551</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -1285,19 +1312,19 @@
         <v>18</v>
       </c>
       <c r="D38" s="1">
-        <v>0.9486252522950128</v>
+        <v>0.94862525229501282</v>
       </c>
       <c r="E38" s="2">
         <v>0.1755803802493838</v>
       </c>
       <c r="F38" s="2">
-        <v>9.80678226218663</v>
+        <v>9.8067822621866299</v>
       </c>
       <c r="G38" s="2">
-        <v>0.0365248092631583</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>3.6524809263158299E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>11</v>
       </c>
@@ -1308,19 +1335,19 @@
         <v>19</v>
       </c>
       <c r="D39" s="1">
-        <v>0.7661393110259188</v>
+        <v>0.76613931102591881</v>
       </c>
       <c r="E39" s="2">
-        <v>0.3131581420723643</v>
+        <v>0.31315814207236431</v>
       </c>
       <c r="F39" s="2">
         <v>2.75779205078473</v>
       </c>
       <c r="G39" s="2">
-        <v>0.0944071353024287</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>9.4407135302428696E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -1331,19 +1358,19 @@
         <v>19</v>
       </c>
       <c r="D40" s="1">
-        <v>0.8800040538136142</v>
+        <v>0.88000405381361424</v>
       </c>
       <c r="E40" s="2">
-        <v>0.045187398810763</v>
+        <v>4.5187398810763002E-2</v>
       </c>
       <c r="F40" s="2">
-        <v>11.65912079377251</v>
+        <v>11.659120793772511</v>
       </c>
       <c r="G40" s="2">
-        <v>-0.0130477609528223</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>-1.30477609528223E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -1354,19 +1381,19 @@
         <v>19</v>
       </c>
       <c r="D41" s="1">
-        <v>0.9083188153726486</v>
+        <v>0.90831881537264858</v>
       </c>
       <c r="E41" s="2">
         <v>0.189565332373659</v>
       </c>
       <c r="F41" s="2">
-        <v>6.43871593806258</v>
+        <v>6.4387159380625798</v>
       </c>
       <c r="G41" s="2">
-        <v>-0.0214684764920969</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>-2.1468476492096902E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -1377,19 +1404,19 @@
         <v>19</v>
       </c>
       <c r="D42" s="1">
-        <v>0.7806258919670035</v>
+        <v>0.78062589196700349</v>
       </c>
       <c r="E42" s="2">
         <v>1.797545304128267</v>
       </c>
       <c r="F42" s="2">
-        <v>0.957806790682215</v>
+        <v>0.95780679068221497</v>
       </c>
       <c r="G42" s="2">
-        <v>0.3253939816695888</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>0.32539398166958883</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -1400,19 +1427,19 @@
         <v>19</v>
       </c>
       <c r="D43" s="1">
-        <v>0.9522157839945232</v>
+        <v>0.95221578399452322</v>
       </c>
       <c r="E43" s="2">
         <v>0.1633092363652788</v>
       </c>
       <c r="F43" s="2">
-        <v>10.7896538489392</v>
+        <v>10.789653848939199</v>
       </c>
       <c r="G43" s="2">
-        <v>0.0100541624939878</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>1.00541624939878E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>12</v>
       </c>
@@ -1423,19 +1450,19 @@
         <v>18</v>
       </c>
       <c r="D44" s="1">
-        <v>0.6308535780427555</v>
+        <v>0.63085357804275555</v>
       </c>
       <c r="E44" s="2">
-        <v>1.108397582077082</v>
+        <v>1.1083975820770819</v>
       </c>
       <c r="F44" s="2">
-        <v>1.183564117480509</v>
+        <v>1.1835641174805089</v>
       </c>
       <c r="G44" s="2">
-        <v>0.3468173805859158</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>0.34681738058591582</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -1446,19 +1473,19 @@
         <v>18</v>
       </c>
       <c r="D45" s="1">
-        <v>0.4633280849885967</v>
+        <v>0.46332808498859668</v>
       </c>
       <c r="E45" s="2">
-        <v>0.4485727806985012</v>
+        <v>0.44857278069850121</v>
       </c>
       <c r="F45" s="2">
-        <v>1.171903204908679</v>
+        <v>1.1719032049086791</v>
       </c>
       <c r="G45" s="2">
-        <v>0.062003812285528</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>6.2003812285528002E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>12</v>
       </c>
@@ -1478,10 +1505,10 @@
         <v>1.629200504248894</v>
       </c>
       <c r="G46" s="2">
-        <v>0.0022907575106107</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>2.2907575106107E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>12</v>
       </c>
@@ -1492,19 +1519,19 @@
         <v>19</v>
       </c>
       <c r="D47" s="1">
-        <v>0.5993544476086745</v>
+        <v>0.59935444760867451</v>
       </c>
       <c r="E47" s="2">
         <v>1.202976746153904</v>
       </c>
       <c r="F47" s="2">
-        <v>1.020145079340591</v>
+        <v>1.0201450793405911</v>
       </c>
       <c r="G47" s="2">
         <v>0.525119971389721</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -1515,19 +1542,19 @@
         <v>19</v>
       </c>
       <c r="D48" s="1">
-        <v>0.5246020342949073</v>
+        <v>0.52460203429490726</v>
       </c>
       <c r="E48" s="2">
-        <v>0.3973574570419117</v>
+        <v>0.39735745704191172</v>
       </c>
       <c r="F48" s="2">
-        <v>1.502848803768949</v>
+        <v>1.5028488037689489</v>
       </c>
       <c r="G48" s="2">
-        <v>0.0603594735885571</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>6.0359473588557103E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>12</v>
       </c>
@@ -1538,19 +1565,24 @@
         <v>19</v>
       </c>
       <c r="D49" s="1">
-        <v>0.7647835344010017</v>
+        <v>0.76478353440100166</v>
       </c>
       <c r="E49" s="2">
-        <v>0.5528864793749785</v>
+        <v>0.55288647937497848</v>
       </c>
       <c r="F49" s="2">
-        <v>2.426337137982781</v>
+        <v>2.4263371379827809</v>
       </c>
       <c r="G49" s="2">
-        <v>0.0423868804416213</v>
+        <v>4.2386880441621297E-2</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D2:D49">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>0.75</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>